--- a/ptcmis-server/src/main/resources/excel-templates/template-stat-inventory-simple.xlsx
+++ b/ptcmis-server/src/main/resources/excel-templates/template-stat-inventory-simple.xlsx
@@ -11,7 +11,7 @@
     <sheet name="库存简报-瓶数" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'库存简报-株数'!$A$3:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'库存简报-株数'!$A$3:$G$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'库存简报-株数'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'库存简报-瓶数'!$1:$3</definedName>
   </definedNames>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>库存简报【株数统计】</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>编号</t>
+  </si>
+  <si>
+    <t>重点品种</t>
   </si>
   <si>
     <t>0代株数</t>
@@ -103,6 +106,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
@@ -166,12 +175,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -811,54 +814,57 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1390,89 +1396,84 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="19.25" style="15" customWidth="1"/>
-    <col min="3" max="3" width="13.3333333333333" style="16" customWidth="1"/>
-    <col min="4" max="6" width="12.75" style="16" customWidth="1"/>
-    <col min="7" max="8" width="12.5" style="16" customWidth="1"/>
+    <col min="1" max="1" width="15.625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="19.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3333333333333" style="17" customWidth="1"/>
+    <col min="5" max="7" width="12.75" style="17" customWidth="1"/>
+    <col min="8" max="9" width="12.5" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:8">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+    <row r="2" ht="24" customHeight="1" spans="1:9">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:8">
-      <c r="A3" s="7" t="s">
+    <row r="3" ht="24" customHeight="1" spans="1:9">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="11" t="s">
         <v>8</v>
       </c>
+      <c r="I3" s="11" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" s="13" customFormat="1" ht="24" customHeight="1" spans="1:8">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="D4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="E4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="F4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="G4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="H4" s="12">
-        <v>99999999999</v>
-      </c>
+    <row r="4" s="15" customFormat="1" ht="24" customHeight="1" spans="1:9">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.251388888888889" right="0.251388888888889" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
@@ -1488,89 +1489,84 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
     <col min="2" max="2" width="19.25" customWidth="1"/>
-    <col min="3" max="3" width="13.3333333333333" customWidth="1"/>
-    <col min="4" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="8" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3333333333333" customWidth="1"/>
+    <col min="5" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="9" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+    <row r="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
     </row>
-    <row r="2" customFormat="1" ht="24" customHeight="1" spans="1:8">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+    <row r="2" customFormat="1" ht="24" customHeight="1" spans="1:9">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:8">
-      <c r="A3" s="7" t="s">
+    <row r="3" ht="24" customHeight="1" spans="1:9">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="11" t="s">
         <v>15</v>
       </c>
+      <c r="I3" s="11" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:8">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="D4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="E4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="F4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="G4" s="12">
-        <v>99999999999</v>
-      </c>
-      <c r="H4" s="12">
-        <v>99999999999</v>
-      </c>
+    <row r="4" ht="24" customHeight="1" spans="1:9">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.251388888888889" right="0.251388888888889" top="0.751388888888889" bottom="0.751388888888889" header="0.298611111111111" footer="0.298611111111111"/>
